--- a/lib/udap_security_test_kit/requirements/hl7.fhir.us.udap-security_1.0.0_reqs.xlsx
+++ b/lib/udap_security_test_kit/requirements/hl7.fhir.us.udap-security_1.0.0_reqs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/knaden/Documents/Inferno/source/udap-security-test-kit/lib/udap_security_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFD8D91-E5E1-0846-9B59-C4F63F2CA645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63112E7-8E83-714E-ABF6-ADE24A6901B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20200" tabRatio="598" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
+    <workbookView xWindow="20" yWindow="800" windowWidth="34560" windowHeight="20100" tabRatio="598" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="9" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="459">
   <si>
     <r>
       <rPr>
@@ -2040,10 +2040,6 @@
     <t>Scope</t>
   </si>
   <si>
-    <t xml:space="preserve">UDAP certification framework wasn't extracted.
-Only 'SHALL" and 'MUST" Statements pulled from UDAP, 'MAY` and `SHOULD` requirements wereincluded prior to new guidance to focus on SHALL and MUST. </t>
-  </si>
-  <si>
     <t>Author</t>
   </si>
   <si>
@@ -2090,216 +2086,6 @@
   </si>
   <si>
     <t>OUT OF SCOPE</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Metadata
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The metadata provides identifying information and context for the collection of requirements. 
-Filling out these fields is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>optional</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-These fields map directly to the R5 Requirements fields.
-Suggested values:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Id: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The requirement set ID. This should be the namespace without version information. See the Info tab for details. For example, for the Da Vinci Drug Formulary v2.0.1, it would be  "hl7.fhir.us.davinci-drug-formulary_2.0.1".
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">URL: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">&lt;inferno base url&gt;/&lt;Name&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Title:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Implementation Guide title / Source document title&gt; Requirements
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: draft
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Publisher:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Inferno
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Copyright:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Licensed under the Apache License, Version 2.0 (the "License"); you may not use this file except in compliance with the License. You may obtain a copy of the License at
-http://www.apache.org/licenses/LICENSE-2.0
-Unless required by applicable law or agreed to in writing, software distributed under the License is distributed on an "AS IS" BASIS, WITHOUT WARRANTIES OR CONDITIONS OF ANY KIND, either express or implied. See the License for the specific language governing permissions and limitations under the License.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Copyright Label: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Copyright (c) &lt;year&gt; The MITRE Corporation
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Reference:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">&lt;Implementation Guide URL&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E.g., for  Da Vinci Payer Data Exchange (v2.0.0: STU2), Reference would be https://hl7.org/fhir/us/davinci-pdex/STU2/.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2736,6 +2522,328 @@
   <si>
     <t>Actors*</t>
   </si>
+  <si>
+    <t>JWT</t>
+  </si>
+  <si>
+    <t>Discovery</t>
+  </si>
+  <si>
+    <t>Tiered Oauth</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Community Parameter</t>
+  </si>
+  <si>
+    <t>Consumer Facing</t>
+  </si>
+  <si>
+    <t>B2B Auth Code</t>
+  </si>
+  <si>
+    <t>B2B Client Credentials</t>
+  </si>
+  <si>
+    <t>B2B Auth Code, Consumer Facing</t>
+  </si>
+  <si>
+    <t>Consumer Facing, B2B Auth Code</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Metadata
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The metadata provides identifying information and context for the collection of requirements. 
+Filling out these fields is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>optional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+These fields map directly to the R5 Requirements fields.
+Suggested values:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Id: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The requirement set ID. This should be the namespace without version information. See the Info tab for details. For example, for the Da Vinci Drug Formulary v2.0.1, it would be  "hl7.fhir.us.davinci-drug-formulary_2.0.1".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">URL: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&lt;inferno base url&gt;/&lt;Name&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Title:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;Implementation Guide title / Source document title&gt; Requirements
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: draft
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Publisher:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Inferno
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Copyright:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Licensed under the Apache License, Version 2.0 (the "License"); you may not use this file except in compliance with the License. You may obtain a copy of the License at
+http://www.apache.org/licenses/LICENSE-2.0
+Unless required by applicable law or agreed to in writing, software distributed under the License is distributed on an "AS IS" BASIS, WITHOUT WARRANTIES OR CONDITIONS OF ANY KIND, either express or implied. See the License for the specific language governing permissions and limitations under the License.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Copyright Label: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Copyright (c) &lt;year&gt; The MITRE Corporation
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reference:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&lt;Implementation Guide URL&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">E.g., for  Da Vinci Payer Data Exchange (v2.0.0: STU2), Reference would be https://hl7.org/fhir/us/davinci-pdex/STU2/.
+Additional metadata:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Scope</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: what requirements were extracted and which were not extracted from the source.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Groupings (Column P)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: definitions of the Groupings in Column P of the Requirements sheet. </t>
+    </r>
+  </si>
+  <si>
+    <t>Groupings (Column P)</t>
+  </si>
+  <si>
+    <t>- JWT: general JWT requirements from the specification home page that apply to clients and servers
+- Discovery: requirements around the discovery of system capabilities.
+- Community Parameter: requirements around the community parameter when performing discovery
+- Registration: requirements around the registration of clients, including using a dynamic API call
+- Tiered OAuth: requirements around tiered OAuth
+- Consumer Facing: requirements for requesting and granting access to users using an authroization code OAuth flow
+- B2B Auth Code: requirements for requesting and granting access to a system using an authorization code OAuth flow
+- B2B Client Credentials: requirements for requesting and granting access to a system using a client credentials OAuth flow</t>
+  </si>
+  <si>
+    <t>B2B Auth Code, Consumer Facing, B2B Client Credentials</t>
+  </si>
+  <si>
+    <t>Consumer Facing, B2B Auth Code, B2B Client Credentials</t>
+  </si>
+  <si>
+    <t>same as 229 - should be collapsed (this url already included there)</t>
+  </si>
+  <si>
+    <t>For grouping, assumes that 172 and 229 are already collapsed so this is a client credentials requirement</t>
+  </si>
+  <si>
+    <t>Same as 172 - should be collapsed into that one or at least have the same subrequirements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDAP certification framework wasn't extracted.
+Only 'SHALL" and 'MUST" Statements pulled from UDAP, 'MAY` and `SHOULD` requirements were included prior to new guidance to focus on SHALL and MUST. </t>
+  </si>
+  <si>
+    <t>for grouping, assume merged with 190, so has B2B Auth code</t>
+  </si>
+  <si>
+    <t>For grouping, has B2B Auth code based on sub-requirements in 190</t>
+  </si>
+  <si>
+    <t>same as 133 - for grouping, assume they are merged</t>
+  </si>
 </sst>
 </file>
 
@@ -3127,7 +3235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3233,6 +3341,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3618,14 +3729,14 @@
       <c r="C3" s="21"/>
     </row>
     <row r="4" spans="1:3" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39" t="s">
-        <v>437</v>
+      <c r="A4" s="40" t="s">
+        <v>435</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="23"/>
     </row>
     <row r="5" spans="1:3" ht="258" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40"/>
+      <c r="A5" s="41"/>
       <c r="B5" s="26"/>
       <c r="C5" s="21"/>
     </row>
@@ -3637,17 +3748,17 @@
       <c r="C6" s="16"/>
     </row>
     <row r="7" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="42"/>
+      <c r="B7" s="43"/>
     </row>
     <row r="8" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="41"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="44"/>
     </row>
     <row r="9" spans="1:3" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="25"/>
     </row>
     <row r="10" spans="1:3" ht="292" x14ac:dyDescent="0.2">
@@ -3708,7 +3819,7 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
@@ -3778,6 +3889,9 @@
       <c r="E2" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="R2" s="5" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="3" spans="1:22" ht="117" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
@@ -3795,6 +3909,9 @@
       <c r="E3" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="R3" s="5" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="4" spans="1:22" ht="117" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
@@ -3811,6 +3928,9 @@
       </c>
       <c r="E4" s="2" t="s">
         <v>31</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:22" s="29" customFormat="1" ht="85" x14ac:dyDescent="0.2">
@@ -3853,7 +3973,9 @@
         <v/>
       </c>
       <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
+      <c r="R5" s="5" t="s">
+        <v>437</v>
+      </c>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -3891,6 +4013,9 @@
         <f t="shared" ref="P6:P13" si="1">IF(ISNUMBER(SEARCH("Server", C6)), "Server", IF(ISNUMBER(SEARCH("client", C6)), "Client", IF(ISNUMBER(SEARCH("Client", C6)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C6)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C6)), "Client", "")))))</f>
         <v/>
       </c>
+      <c r="R6" s="5" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="7" spans="1:22" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
@@ -3924,6 +4049,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
+      <c r="R7" s="5" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="8" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
@@ -3941,6 +4069,9 @@
       <c r="E8" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="R8" s="5" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="9" spans="1:22" ht="238" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -3958,6 +4089,9 @@
       <c r="E9" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="R9" s="5" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="10" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -3991,6 +4125,9 @@
         <f t="shared" si="1"/>
         <v>Server</v>
       </c>
+      <c r="R10" s="5" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="11" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -4024,6 +4161,9 @@
         <f t="shared" si="1"/>
         <v>Server</v>
       </c>
+      <c r="R11" s="5" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="12" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -4057,6 +4197,9 @@
         <f t="shared" si="1"/>
         <v>Server</v>
       </c>
+      <c r="R12" s="5" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="13" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -4090,6 +4233,9 @@
         <f t="shared" si="1"/>
         <v>Server</v>
       </c>
+      <c r="R13" s="5" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="14" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -4123,6 +4269,9 @@
         <f>IF(ISNUMBER(SEARCH("Server", C14)), "Server", IF(ISNUMBER(SEARCH("client", C14)), "Client", IF(ISNUMBER(SEARCH("Client", C14)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C14)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C14)), "Client", "")))))</f>
         <v>Server</v>
       </c>
+      <c r="R14" s="5" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="15" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -4156,6 +4305,9 @@
         <f t="shared" ref="P15:P23" si="2">IF(ISNUMBER(SEARCH("Server", C15)), "Server", IF(ISNUMBER(SEARCH("client", C15)), "Client", IF(ISNUMBER(SEARCH("Client", C15)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C15)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C15)), "Client", "")))))</f>
         <v>Server</v>
       </c>
+      <c r="R15" s="5" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="16" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -4189,11 +4341,14 @@
         <f t="shared" si="2"/>
         <v>Server</v>
       </c>
+      <c r="R16" s="5" t="s">
+        <v>438</v>
+      </c>
       <c r="V16" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -4225,8 +4380,11 @@
         <f t="shared" si="2"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R17" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4258,8 +4416,11 @@
         <f t="shared" si="2"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R18" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -4291,8 +4452,11 @@
         <f t="shared" si="2"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R19" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4324,8 +4488,11 @@
         <f t="shared" si="2"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R20" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4357,8 +4524,11 @@
         <f t="shared" si="2"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R21" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4390,8 +4560,11 @@
         <f t="shared" si="2"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R22" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4423,8 +4596,11 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R23" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4456,8 +4632,11 @@
         <f t="shared" ref="P24:P59" si="3">IF(ISNUMBER(SEARCH("server", C24)), "Server", IF(ISNUMBER(SEARCH("Server", C24)), "Server", IF(ISNUMBER(SEARCH("client", C24)), "Client", IF(ISNUMBER(SEARCH("Client", C24)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C24)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C24)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R24" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4495,8 +4674,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R25" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4534,8 +4716,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R26" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4573,8 +4758,11 @@
         <f t="shared" si="3"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+      <c r="R27" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="204" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4612,8 +4800,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R28" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4645,8 +4836,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+      <c r="R29" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4678,8 +4872,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C30)), "Server", IF(ISNUMBER(SEARCH("Server", C30)), "Server", IF(ISNUMBER(SEARCH("client", C30)), "Client", IF(ISNUMBER(SEARCH("Client", C30)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C30)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C30)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R30" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4711,8 +4908,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R31" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -4744,8 +4944,11 @@
         <f t="shared" ref="P32" si="5">IF(ISNUMBER(SEARCH("server", C32)), "Server", IF(ISNUMBER(SEARCH("Server", C32)), "Server", IF(ISNUMBER(SEARCH("client", C32)), "Client", IF(ISNUMBER(SEARCH("Client", C32)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C32)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C32)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R32" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -4777,8 +4980,11 @@
         <f t="shared" ref="P33" si="7">IF(ISNUMBER(SEARCH("server", C33)), "Server", IF(ISNUMBER(SEARCH("Server", C33)), "Server", IF(ISNUMBER(SEARCH("client", C33)), "Client", IF(ISNUMBER(SEARCH("Client", C33)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C33)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C33)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+      <c r="R33" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -4810,8 +5016,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R34" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -4843,8 +5052,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R35" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -4876,8 +5088,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C36)), "Server", IF(ISNUMBER(SEARCH("Server", C36)), "Server", IF(ISNUMBER(SEARCH("client", C36)), "Client", IF(ISNUMBER(SEARCH("Client", C36)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C36)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C36)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R36" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -4909,8 +5124,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R37" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -4942,8 +5160,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C38)), "Server", IF(ISNUMBER(SEARCH("Server", C38)), "Server", IF(ISNUMBER(SEARCH("client", C38)), "Client", IF(ISNUMBER(SEARCH("Client", C38)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C38)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C38)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R38" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -4981,8 +5202,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R39" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -5020,8 +5244,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C40)), "Server", IF(ISNUMBER(SEARCH("Server", C40)), "Server", IF(ISNUMBER(SEARCH("client", C40)), "Client", IF(ISNUMBER(SEARCH("Client", C40)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C40)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C40)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="41" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R40" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -5053,8 +5280,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R41" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5086,8 +5316,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R42" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -5119,8 +5352,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R43" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -5152,8 +5388,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R44" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -5185,8 +5424,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+      <c r="R45" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -5224,8 +5466,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C46)), "Server", IF(ISNUMBER(SEARCH("Server", C46)), "Server", IF(ISNUMBER(SEARCH("client", C46)), "Client", IF(ISNUMBER(SEARCH("Client", C46)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C46)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C46)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R46" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -5257,8 +5502,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R47" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -5290,8 +5538,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R48" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -5323,8 +5574,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C49)), "Server", IF(ISNUMBER(SEARCH("Server", C49)), "Server", IF(ISNUMBER(SEARCH("client", C49)), "Client", IF(ISNUMBER(SEARCH("Client", C49)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C49)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C49)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R49" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -5356,8 +5610,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C50)), "Server", IF(ISNUMBER(SEARCH("Server", C50)), "Server", IF(ISNUMBER(SEARCH("client", C50)), "Client", IF(ISNUMBER(SEARCH("Client", C50)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C50)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C50)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R50" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -5389,8 +5646,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C51)), "Server", IF(ISNUMBER(SEARCH("Server", C51)), "Server", IF(ISNUMBER(SEARCH("client", C51)), "Client", IF(ISNUMBER(SEARCH("Client", C51)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C51)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C51)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R51" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -5422,8 +5682,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R52" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -5455,8 +5718,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R53" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -5488,8 +5754,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C54)), "Server", IF(ISNUMBER(SEARCH("Server", C54)), "Server", IF(ISNUMBER(SEARCH("client", C54)), "Client", IF(ISNUMBER(SEARCH("Client", C54)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C54)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C54)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R54" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -5521,8 +5790,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R55" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -5554,8 +5826,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R56" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -5587,8 +5862,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C57)), "Server", IF(ISNUMBER(SEARCH("Server", C57)), "Server", IF(ISNUMBER(SEARCH("client", C57)), "Client", IF(ISNUMBER(SEARCH("Client", C57)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C57)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C57)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R57" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -5620,8 +5898,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R58" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -5653,8 +5934,11 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R59" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -5686,8 +5970,11 @@
         <f t="shared" ref="P60:P67" si="9">IF(ISNUMBER(SEARCH("server", C60)), "Server", IF(ISNUMBER(SEARCH("Server", C60)), "Server", IF(ISNUMBER(SEARCH("client", C60)), "Client", IF(ISNUMBER(SEARCH("Client", C60)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C60)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C60)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R60" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -5719,8 +6006,11 @@
         <f t="shared" si="9"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R61" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -5752,8 +6042,11 @@
         <f t="shared" si="9"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="R62" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -5785,8 +6078,11 @@
         <f t="shared" ref="P63" si="11">IF(ISNUMBER(SEARCH("server", C63)), "Server", IF(ISNUMBER(SEARCH("Server", C63)), "Server", IF(ISNUMBER(SEARCH("client", C63)), "Client", IF(ISNUMBER(SEARCH("Client", C63)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C63)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C63)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R63" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -5818,8 +6114,11 @@
         <f t="shared" ref="P64:P65" si="13">IF(ISNUMBER(SEARCH("server", C64)), "Server", IF(ISNUMBER(SEARCH("Server", C64)), "Server", IF(ISNUMBER(SEARCH("client", C64)), "Client", IF(ISNUMBER(SEARCH("Client", C64)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C64)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C64)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="170" x14ac:dyDescent="0.2">
+      <c r="R64" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="170" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -5851,8 +6150,11 @@
         <f t="shared" si="13"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R65" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -5884,8 +6186,11 @@
         <f t="shared" ref="P66" si="15">IF(ISNUMBER(SEARCH("server", C66)), "Server", IF(ISNUMBER(SEARCH("Server", C66)), "Server", IF(ISNUMBER(SEARCH("client", C66)), "Client", IF(ISNUMBER(SEARCH("Client", C66)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C66)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C66)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R66" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -5917,8 +6222,11 @@
         <f t="shared" si="9"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R67" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -5950,8 +6258,11 @@
         <f t="shared" ref="P68" si="17">IF(ISNUMBER(SEARCH("server", C68)), "Server", IF(ISNUMBER(SEARCH("Server", C68)), "Server", IF(ISNUMBER(SEARCH("client", C68)), "Client", IF(ISNUMBER(SEARCH("Client", C68)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C68)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C68)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R68" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -5983,8 +6294,11 @@
         <f t="shared" ref="P69:P115" si="19">IF(ISNUMBER(SEARCH("server", C69)), "Server", IF(ISNUMBER(SEARCH("Server", C69)), "Server", IF(ISNUMBER(SEARCH("client", C69)), "Client", IF(ISNUMBER(SEARCH("Client", C69)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C69)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C69)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R69" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -6016,8 +6330,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R70" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -6049,8 +6366,11 @@
         <f t="shared" si="19"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R71" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -6074,8 +6394,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C72)), "Server", IF(ISNUMBER(SEARCH("Server", C72)), "Server", IF(ISNUMBER(SEARCH("client", C72)), "Client", IF(ISNUMBER(SEARCH("Client", C72)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C72)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C72)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R72" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -6110,8 +6433,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R73" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -6143,8 +6469,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R74" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -6176,8 +6505,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C75)), "Server", IF(ISNUMBER(SEARCH("Server", C75)), "Server", IF(ISNUMBER(SEARCH("client", C75)), "Client", IF(ISNUMBER(SEARCH("Client", C75)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C75)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C75)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R75" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -6209,8 +6541,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R76" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -6242,8 +6577,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="78" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R77" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -6275,8 +6613,11 @@
         <f t="shared" si="19"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R78" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -6308,8 +6649,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="80" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R79" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -6341,8 +6685,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C80)), "Server", IF(ISNUMBER(SEARCH("Server", C80)), "Server", IF(ISNUMBER(SEARCH("client", C80)), "Client", IF(ISNUMBER(SEARCH("Client", C80)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C80)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C80)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="81" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R80" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -6374,8 +6721,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="82" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R81" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -6407,8 +6757,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="83" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R82" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -6440,8 +6793,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C83)), "Server", IF(ISNUMBER(SEARCH("Server", C83)), "Server", IF(ISNUMBER(SEARCH("client", C83)), "Client", IF(ISNUMBER(SEARCH("Client", C83)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C83)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C83)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R83" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -6473,8 +6829,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R84" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -6506,8 +6865,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="86" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R85" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -6539,8 +6901,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="87" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R86" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -6572,8 +6937,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="88" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R87" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -6605,8 +6973,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C88)), "Server", IF(ISNUMBER(SEARCH("Server", C88)), "Server", IF(ISNUMBER(SEARCH("client", C88)), "Client", IF(ISNUMBER(SEARCH("Client", C88)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C88)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C88)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="89" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R88" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -6638,8 +7009,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R89" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -6671,8 +7045,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C90)), "Server", IF(ISNUMBER(SEARCH("Server", C90)), "Server", IF(ISNUMBER(SEARCH("client", C90)), "Client", IF(ISNUMBER(SEARCH("Client", C90)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C90)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C90)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R90" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -6704,8 +7081,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C91)), "Server", IF(ISNUMBER(SEARCH("Server", C91)), "Server", IF(ISNUMBER(SEARCH("client", C91)), "Client", IF(ISNUMBER(SEARCH("Client", C91)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C91)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C91)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="92" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R91" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -6737,8 +7117,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C92)), "Server", IF(ISNUMBER(SEARCH("Server", C92)), "Server", IF(ISNUMBER(SEARCH("client", C92)), "Client", IF(ISNUMBER(SEARCH("Client", C92)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C92)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C92)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="93" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R92" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -6770,8 +7153,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R93" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -6803,8 +7189,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="95" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R94" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -6836,8 +7225,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C95)), "Server", IF(ISNUMBER(SEARCH("Server", C95)), "Server", IF(ISNUMBER(SEARCH("client", C95)), "Client", IF(ISNUMBER(SEARCH("Client", C95)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C95)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C95)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="96" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R95" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -6869,8 +7261,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="97" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R96" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -6902,8 +7297,11 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-    </row>
-    <row r="98" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R97" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -6935,8 +7333,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R98" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -6968,8 +7369,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C99)), "Server", IF(ISNUMBER(SEARCH("Server", C99)), "Server", IF(ISNUMBER(SEARCH("client", C99)), "Client", IF(ISNUMBER(SEARCH("Client", C99)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C99)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C99)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R99" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -7001,8 +7405,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C100)), "Server", IF(ISNUMBER(SEARCH("Server", C100)), "Server", IF(ISNUMBER(SEARCH("client", C100)), "Client", IF(ISNUMBER(SEARCH("Client", C100)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C100)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C100)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R100" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -7034,8 +7441,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C101)), "Server", IF(ISNUMBER(SEARCH("Server", C101)), "Server", IF(ISNUMBER(SEARCH("client", C101)), "Client", IF(ISNUMBER(SEARCH("Client", C101)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C101)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C101)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R101" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -7067,8 +7477,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R102" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -7100,8 +7513,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R103" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -7133,8 +7549,11 @@
         <f t="shared" si="19"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R104" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -7166,8 +7585,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C105)), "Server", IF(ISNUMBER(SEARCH("Server", C105)), "Server", IF(ISNUMBER(SEARCH("client", C105)), "Client", IF(ISNUMBER(SEARCH("Client", C105)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C105)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C105)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R105" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -7199,8 +7621,11 @@
         <f t="shared" si="19"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R106" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -7224,8 +7649,11 @@
         <f t="shared" si="19"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="R107" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -7249,8 +7677,11 @@
         <f t="shared" ref="P108" si="21">IF(ISNUMBER(SEARCH("server", C108)), "Server", IF(ISNUMBER(SEARCH("Server", C108)), "Server", IF(ISNUMBER(SEARCH("client", C108)), "Client", IF(ISNUMBER(SEARCH("Client", C108)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C108)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C108)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="109" spans="1:16" ht="112.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R108" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="112.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -7274,8 +7705,11 @@
         <f t="shared" ref="P109" si="23">IF(ISNUMBER(SEARCH("server", C109)), "Server", IF(ISNUMBER(SEARCH("Server", C109)), "Server", IF(ISNUMBER(SEARCH("client", C109)), "Client", IF(ISNUMBER(SEARCH("Client", C109)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C109)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C109)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" ht="112.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R109" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="112.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -7299,8 +7733,11 @@
         <f t="shared" ref="P110" si="25">IF(ISNUMBER(SEARCH("server", C110)), "Server", IF(ISNUMBER(SEARCH("Server", C110)), "Server", IF(ISNUMBER(SEARCH("client", C110)), "Client", IF(ISNUMBER(SEARCH("Client", C110)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C110)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C110)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="111" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="R110" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -7332,8 +7769,11 @@
         <f t="shared" si="19"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R111" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -7365,8 +7805,11 @@
         <f t="shared" ref="P112" si="27">IF(ISNUMBER(SEARCH("server", C112)), "Server", IF(ISNUMBER(SEARCH("Server", C112)), "Server", IF(ISNUMBER(SEARCH("client", C112)), "Client", IF(ISNUMBER(SEARCH("Client", C112)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C112)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C112)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R112" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -7398,8 +7841,11 @@
         <f t="shared" ref="P113" si="29">IF(ISNUMBER(SEARCH("server", C113)), "Server", IF(ISNUMBER(SEARCH("Server", C113)), "Server", IF(ISNUMBER(SEARCH("client", C113)), "Client", IF(ISNUMBER(SEARCH("Client", C113)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C113)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C113)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="114" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R113" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -7431,8 +7877,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C114)), "Server", IF(ISNUMBER(SEARCH("Server", C114)), "Server", IF(ISNUMBER(SEARCH("client", C114)), "Client", IF(ISNUMBER(SEARCH("Client", C114)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C114)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C114)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="115" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="R114" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -7464,8 +7913,11 @@
         <f t="shared" si="19"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="116" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+      <c r="R115" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -7473,8 +7925,11 @@
       <c r="D116" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="117" spans="1:16" ht="80" x14ac:dyDescent="0.2">
+      <c r="R116" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" ht="80" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -7506,8 +7961,11 @@
         <f t="shared" ref="P117" si="31">IF(ISNUMBER(SEARCH("server", C117)), "Server", IF(ISNUMBER(SEARCH("Server", C117)), "Server", IF(ISNUMBER(SEARCH("client", C117)), "Client", IF(ISNUMBER(SEARCH("Client", C117)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C117)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C117)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="118" spans="1:16" ht="80" x14ac:dyDescent="0.2">
+      <c r="R117" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" ht="80" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -7539,8 +7997,11 @@
         <f t="shared" ref="P118:P119" si="33">IF(ISNUMBER(SEARCH("server", C118)), "Server", IF(ISNUMBER(SEARCH("Server", C118)), "Server", IF(ISNUMBER(SEARCH("client", C118)), "Client", IF(ISNUMBER(SEARCH("Client", C118)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C118)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C118)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R118" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -7572,8 +8033,11 @@
         <f t="shared" si="33"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+      <c r="R119" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" ht="204" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -7605,8 +8069,11 @@
         <f t="shared" ref="P120" si="35">IF(ISNUMBER(SEARCH("server", C120)), "Server", IF(ISNUMBER(SEARCH("Server", C120)), "Server", IF(ISNUMBER(SEARCH("client", C120)), "Client", IF(ISNUMBER(SEARCH("Client", C120)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C120)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C120)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R120" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -7638,8 +8105,11 @@
         <f t="shared" ref="P121" si="37">IF(ISNUMBER(SEARCH("server", C121)), "Server", IF(ISNUMBER(SEARCH("Server", C121)), "Server", IF(ISNUMBER(SEARCH("client", C121)), "Client", IF(ISNUMBER(SEARCH("Client", C121)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C121)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C121)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="122" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R121" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -7671,8 +8141,11 @@
         <f t="shared" ref="P122" si="39">IF(ISNUMBER(SEARCH("server", C122)), "Server", IF(ISNUMBER(SEARCH("Server", C122)), "Server", IF(ISNUMBER(SEARCH("client", C122)), "Client", IF(ISNUMBER(SEARCH("Client", C122)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C122)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C122)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="123" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R122" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -7704,8 +8177,11 @@
         <f t="shared" ref="P123" si="41">IF(ISNUMBER(SEARCH("server", C123)), "Server", IF(ISNUMBER(SEARCH("Server", C123)), "Server", IF(ISNUMBER(SEARCH("client", C123)), "Client", IF(ISNUMBER(SEARCH("Client", C123)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C123)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C123)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="124" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R123" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -7737,8 +8213,11 @@
         <f t="shared" ref="P124" si="43">IF(ISNUMBER(SEARCH("server", C124)), "Server", IF(ISNUMBER(SEARCH("Server", C124)), "Server", IF(ISNUMBER(SEARCH("client", C124)), "Client", IF(ISNUMBER(SEARCH("Client", C124)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C124)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C124)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="125" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R124" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -7770,8 +8249,11 @@
         <f t="shared" ref="P125" si="45">IF(ISNUMBER(SEARCH("server", C125)), "Server", IF(ISNUMBER(SEARCH("Server", C125)), "Server", IF(ISNUMBER(SEARCH("client", C125)), "Client", IF(ISNUMBER(SEARCH("Client", C125)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C125)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C125)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="126" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R125" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -7803,8 +8285,11 @@
         <f t="shared" ref="P126" si="47">IF(ISNUMBER(SEARCH("server", C126)), "Server", IF(ISNUMBER(SEARCH("Server", C126)), "Server", IF(ISNUMBER(SEARCH("client", C126)), "Client", IF(ISNUMBER(SEARCH("Client", C126)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C126)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C126)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="127" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R126" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -7836,8 +8321,11 @@
         <f t="shared" ref="P127:P203" si="49">IF(ISNUMBER(SEARCH("server", C127)), "Server", IF(ISNUMBER(SEARCH("Server", C127)), "Server", IF(ISNUMBER(SEARCH("client", C127)), "Client", IF(ISNUMBER(SEARCH("Client", C127)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C127)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C127)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="128" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R127" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -7872,8 +8360,11 @@
         <f t="shared" ref="P128:P129" si="51">IF(ISNUMBER(SEARCH("server", C128)), "Server", IF(ISNUMBER(SEARCH("Server", C128)), "Server", IF(ISNUMBER(SEARCH("client", C128)), "Client", IF(ISNUMBER(SEARCH("Client", C128)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C128)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C128)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R128" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -7897,8 +8388,11 @@
         <f t="shared" si="51"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R129" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -7922,8 +8416,11 @@
         <f t="shared" ref="P130" si="53">IF(ISNUMBER(SEARCH("server", C130)), "Server", IF(ISNUMBER(SEARCH("Server", C130)), "Server", IF(ISNUMBER(SEARCH("client", C130)), "Client", IF(ISNUMBER(SEARCH("Client", C130)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C130)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C130)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="131" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R130" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -7955,8 +8452,11 @@
         <f t="shared" ref="P131" si="55">IF(ISNUMBER(SEARCH("server", C131)), "Server", IF(ISNUMBER(SEARCH("Server", C131)), "Server", IF(ISNUMBER(SEARCH("client", C131)), "Client", IF(ISNUMBER(SEARCH("Client", C131)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C131)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C131)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="132" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R131" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -7988,8 +8488,11 @@
         <f t="shared" ref="P132" si="57">IF(ISNUMBER(SEARCH("server", C132)), "Server", IF(ISNUMBER(SEARCH("Server", C132)), "Server", IF(ISNUMBER(SEARCH("client", C132)), "Client", IF(ISNUMBER(SEARCH("Client", C132)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C132)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C132)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R132" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -8021,8 +8524,11 @@
         <f t="shared" ref="P133" si="59">IF(ISNUMBER(SEARCH("server", C133)), "Server", IF(ISNUMBER(SEARCH("Server", C133)), "Server", IF(ISNUMBER(SEARCH("client", C133)), "Client", IF(ISNUMBER(SEARCH("Client", C133)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C133)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C133)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="134" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R133" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -8057,8 +8563,14 @@
         <f t="shared" ref="P134" si="61">IF(ISNUMBER(SEARCH("server", C134)), "Server", IF(ISNUMBER(SEARCH("Server", C134)), "Server", IF(ISNUMBER(SEARCH("client", C134)), "Client", IF(ISNUMBER(SEARCH("Client", C134)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C134)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C134)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="135" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R134" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V134" s="5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -8090,8 +8602,14 @@
         <f t="shared" ref="P135" si="63">IF(ISNUMBER(SEARCH("server", C135)), "Server", IF(ISNUMBER(SEARCH("Server", C135)), "Server", IF(ISNUMBER(SEARCH("client", C135)), "Client", IF(ISNUMBER(SEARCH("Client", C135)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C135)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C135)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="136" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R135" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V135" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -8123,8 +8641,14 @@
         <f t="shared" ref="P136" si="65">IF(ISNUMBER(SEARCH("server", C136)), "Server", IF(ISNUMBER(SEARCH("Server", C136)), "Server", IF(ISNUMBER(SEARCH("client", C136)), "Client", IF(ISNUMBER(SEARCH("Client", C136)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C136)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C136)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="137" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R136" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V136" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -8156,8 +8680,14 @@
         <f t="shared" ref="P137" si="67">IF(ISNUMBER(SEARCH("server", C137)), "Server", IF(ISNUMBER(SEARCH("Server", C137)), "Server", IF(ISNUMBER(SEARCH("client", C137)), "Client", IF(ISNUMBER(SEARCH("Client", C137)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C137)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C137)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="138" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="R137" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V137" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -8189,8 +8719,14 @@
         <f t="shared" ref="P138:P139" si="69">IF(ISNUMBER(SEARCH("server", C138)), "Server", IF(ISNUMBER(SEARCH("Server", C138)), "Server", IF(ISNUMBER(SEARCH("client", C138)), "Client", IF(ISNUMBER(SEARCH("Client", C138)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C138)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C138)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="139" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R138" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V138" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -8222,8 +8758,14 @@
         <f t="shared" si="69"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="140" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R139" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V139" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22" ht="51" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -8255,8 +8797,14 @@
         <f t="shared" ref="P140" si="71">IF(ISNUMBER(SEARCH("server", C140)), "Server", IF(ISNUMBER(SEARCH("Server", C140)), "Server", IF(ISNUMBER(SEARCH("client", C140)), "Client", IF(ISNUMBER(SEARCH("Client", C140)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C140)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C140)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="141" spans="1:16" ht="160" x14ac:dyDescent="0.2">
+      <c r="R140" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V140" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="141" spans="1:22" ht="160" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -8289,8 +8837,11 @@
         <f t="shared" si="49"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="142" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R141" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="142" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -8314,8 +8865,11 @@
         <f t="shared" ref="P142:P151" si="73">IF(ISNUMBER(SEARCH("server", C142)), "Server", IF(ISNUMBER(SEARCH("Server", C142)), "Server", IF(ISNUMBER(SEARCH("client", C142)), "Client", IF(ISNUMBER(SEARCH("Client", C142)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C142)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C142)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="143" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R142" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -8339,8 +8893,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="144" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R143" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -8367,8 +8924,11 @@
         <f t="shared" si="73"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="145" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="R144" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -8392,8 +8952,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="146" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="R145" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -8417,8 +8980,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="147" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R146" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -8442,8 +9008,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="148" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R147" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -8467,8 +9036,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="149" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R148" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -8492,8 +9064,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="150" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R149" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -8517,8 +9092,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="151" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+      <c r="R150" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -8542,8 +9120,11 @@
         <f t="shared" si="73"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="152" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+      <c r="R151" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" ht="153" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -8575,8 +9156,11 @@
         <f t="shared" si="49"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="153" spans="1:16" ht="64" x14ac:dyDescent="0.2">
+      <c r="R152" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -8608,8 +9192,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C153)), "Server", IF(ISNUMBER(SEARCH("Server", C153)), "Server", IF(ISNUMBER(SEARCH("client", C153)), "Client", IF(ISNUMBER(SEARCH("Client", C153)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C153)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C153)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="154" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R153" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -8641,8 +9228,11 @@
         <f t="shared" ref="P154" si="75">IF(ISNUMBER(SEARCH("server", C154)), "Server", IF(ISNUMBER(SEARCH("Server", C154)), "Server", IF(ISNUMBER(SEARCH("client", C154)), "Client", IF(ISNUMBER(SEARCH("Client", C154)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C154)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C154)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="155" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R154" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -8674,8 +9264,11 @@
         <f t="shared" ref="P155:P158" si="77">IF(ISNUMBER(SEARCH("server", C155)), "Server", IF(ISNUMBER(SEARCH("Server", C155)), "Server", IF(ISNUMBER(SEARCH("client", C155)), "Client", IF(ISNUMBER(SEARCH("Client", C155)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C155)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C155)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="156" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R155" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -8707,8 +9300,11 @@
         <f t="shared" si="77"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="157" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R156" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -8740,8 +9336,11 @@
         <f t="shared" si="77"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="158" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R157" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -8773,8 +9372,11 @@
         <f t="shared" si="77"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="159" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R158" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -8806,8 +9408,11 @@
         <f t="shared" ref="P159" si="79">IF(ISNUMBER(SEARCH("server", C159)), "Server", IF(ISNUMBER(SEARCH("Server", C159)), "Server", IF(ISNUMBER(SEARCH("client", C159)), "Client", IF(ISNUMBER(SEARCH("Client", C159)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C159)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C159)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="160" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R159" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -8839,8 +9444,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C160)), "Server", IF(ISNUMBER(SEARCH("Server", C160)), "Server", IF(ISNUMBER(SEARCH("client", C160)), "Client", IF(ISNUMBER(SEARCH("Client", C160)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C160)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C160)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="161" spans="1:16" ht="220.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R160" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="161" spans="1:22" ht="220.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -8872,8 +9480,11 @@
         <f t="shared" ref="P161" si="81">IF(ISNUMBER(SEARCH("server", C161)), "Server", IF(ISNUMBER(SEARCH("Server", C161)), "Server", IF(ISNUMBER(SEARCH("client", C161)), "Client", IF(ISNUMBER(SEARCH("Client", C161)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C161)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C161)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="162" spans="1:16" ht="131.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R161" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="162" spans="1:22" ht="131.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -8905,8 +9516,11 @@
         <f t="shared" ref="P162" si="83">IF(ISNUMBER(SEARCH("server", C162)), "Server", IF(ISNUMBER(SEARCH("Server", C162)), "Server", IF(ISNUMBER(SEARCH("client", C162)), "Client", IF(ISNUMBER(SEARCH("Client", C162)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C162)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C162)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="163" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R162" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="163" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -8941,8 +9555,11 @@
         <f t="shared" si="49"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="164" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+      <c r="R163" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="164" spans="1:22" ht="153" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -8974,8 +9591,11 @@
         <f t="shared" ref="P164" si="85">IF(ISNUMBER(SEARCH("server", C164)), "Server", IF(ISNUMBER(SEARCH("Server", C164)), "Server", IF(ISNUMBER(SEARCH("client", C164)), "Client", IF(ISNUMBER(SEARCH("Client", C164)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C164)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C164)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="165" spans="1:16" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R164" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="165" spans="1:22" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -9007,8 +9627,11 @@
         <f t="shared" ref="P165" si="87">IF(ISNUMBER(SEARCH("server", C165)), "Server", IF(ISNUMBER(SEARCH("Server", C165)), "Server", IF(ISNUMBER(SEARCH("client", C165)), "Client", IF(ISNUMBER(SEARCH("Client", C165)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C165)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C165)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="166" spans="1:16" ht="133.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R165" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="166" spans="1:22" ht="133.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -9040,8 +9663,11 @@
         <f t="shared" ref="P166" si="89">IF(ISNUMBER(SEARCH("server", C166)), "Server", IF(ISNUMBER(SEARCH("Server", C166)), "Server", IF(ISNUMBER(SEARCH("client", C166)), "Client", IF(ISNUMBER(SEARCH("Client", C166)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C166)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C166)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="167" spans="1:16" ht="119.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R166" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="167" spans="1:22" ht="119.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -9073,8 +9699,11 @@
         <f t="shared" ref="P167" si="91">IF(ISNUMBER(SEARCH("server", C167)), "Server", IF(ISNUMBER(SEARCH("Server", C167)), "Server", IF(ISNUMBER(SEARCH("client", C167)), "Client", IF(ISNUMBER(SEARCH("Client", C167)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C167)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C167)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="168" spans="1:16" ht="128" x14ac:dyDescent="0.2">
+      <c r="R167" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="168" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -9106,8 +9735,11 @@
         <f t="shared" ref="P168" si="93">IF(ISNUMBER(SEARCH("server", C168)), "Server", IF(ISNUMBER(SEARCH("Server", C168)), "Server", IF(ISNUMBER(SEARCH("client", C168)), "Client", IF(ISNUMBER(SEARCH("Client", C168)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C168)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C168)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="169" spans="1:16" ht="128" x14ac:dyDescent="0.2">
+      <c r="R168" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="169" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -9139,8 +9771,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C169)), "Server", IF(ISNUMBER(SEARCH("Server", C169)), "Server", IF(ISNUMBER(SEARCH("client", C169)), "Client", IF(ISNUMBER(SEARCH("Client", C169)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C169)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C169)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="170" spans="1:16" ht="128" x14ac:dyDescent="0.2">
+      <c r="R169" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="170" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -9172,8 +9807,11 @@
         <f t="shared" ref="P170" si="95">IF(ISNUMBER(SEARCH("server", C170)), "Server", IF(ISNUMBER(SEARCH("Server", C170)), "Server", IF(ISNUMBER(SEARCH("client", C170)), "Client", IF(ISNUMBER(SEARCH("Client", C170)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C170)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C170)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="171" spans="1:16" ht="128" x14ac:dyDescent="0.2">
+      <c r="R170" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="171" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -9205,8 +9843,11 @@
         <f t="shared" ref="P171" si="97">IF(ISNUMBER(SEARCH("server", C171)), "Server", IF(ISNUMBER(SEARCH("Server", C171)), "Server", IF(ISNUMBER(SEARCH("client", C171)), "Client", IF(ISNUMBER(SEARCH("Client", C171)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C171)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C171)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="172" spans="1:16" ht="128" x14ac:dyDescent="0.2">
+      <c r="R171" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="172" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -9238,8 +9879,11 @@
         <f t="shared" ref="P172" si="99">IF(ISNUMBER(SEARCH("server", C172)), "Server", IF(ISNUMBER(SEARCH("Server", C172)), "Server", IF(ISNUMBER(SEARCH("client", C172)), "Client", IF(ISNUMBER(SEARCH("Client", C172)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C172)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C172)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="173" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R172" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="173" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -9274,8 +9918,14 @@
         <f t="shared" ref="P173" si="101">IF(ISNUMBER(SEARCH("server", C173)), "Server", IF(ISNUMBER(SEARCH("Server", C173)), "Server", IF(ISNUMBER(SEARCH("client", C173)), "Client", IF(ISNUMBER(SEARCH("Client", C173)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C173)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C173)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="174" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R173" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V173" s="5" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="174" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -9299,8 +9949,14 @@
         <f>IF(ISNUMBER(SEARCH("server", C174)), "Server", IF(ISNUMBER(SEARCH("Server", C174)), "Server", IF(ISNUMBER(SEARCH("client", C174)), "Client", IF(ISNUMBER(SEARCH("Client", C174)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C174)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C174)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="175" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="R174" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V174" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="175" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>174</v>
       </c>
@@ -9324,8 +9980,14 @@
         <f>IF(ISNUMBER(SEARCH("server", C175)), "Server", IF(ISNUMBER(SEARCH("Server", C175)), "Server", IF(ISNUMBER(SEARCH("client", C175)), "Client", IF(ISNUMBER(SEARCH("Client", C175)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C175)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C175)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="176" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R175" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V175" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="176" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -9349,8 +10011,14 @@
         <f>IF(ISNUMBER(SEARCH("server", C176)), "Server", IF(ISNUMBER(SEARCH("Server", C176)), "Server", IF(ISNUMBER(SEARCH("client", C176)), "Client", IF(ISNUMBER(SEARCH("Client", C176)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C176)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C176)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+      <c r="R176" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V176" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="177" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -9373,6 +10041,12 @@
       <c r="P177" s="5" t="str">
         <f>IF(ISNUMBER(SEARCH("server", C177)), "Server", IF(ISNUMBER(SEARCH("Server", C177)), "Server", IF(ISNUMBER(SEARCH("client", C177)), "Client", IF(ISNUMBER(SEARCH("Client", C177)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C177)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C177)), "Client", ""))))))</f>
         <v/>
+      </c>
+      <c r="R177" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V177" s="5" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="178" spans="1:22" ht="136" x14ac:dyDescent="0.2">
@@ -9399,8 +10073,14 @@
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="179" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+      <c r="R178" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V178" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="179" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>178</v>
       </c>
@@ -9424,8 +10104,14 @@
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="180" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+      <c r="R179" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V179" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="180" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -9449,8 +10135,14 @@
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="181" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+      <c r="R180" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V180" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="181" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>180</v>
       </c>
@@ -9474,8 +10166,14 @@
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="182" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+      <c r="R181" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V181" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="182" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -9499,8 +10197,14 @@
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="183" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+      <c r="R182" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V182" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="183" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>182</v>
       </c>
@@ -9524,8 +10228,14 @@
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="184" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R183" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V183" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="184" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -9548,6 +10258,12 @@
       <c r="P184" s="5" t="str">
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
+      </c>
+      <c r="R184" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="V184" s="5" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:22" ht="128" x14ac:dyDescent="0.2">
@@ -9582,6 +10298,9 @@
         <f t="shared" ref="P185" si="103">IF(ISNUMBER(SEARCH("server", C185)), "Server", IF(ISNUMBER(SEARCH("Server", C185)), "Server", IF(ISNUMBER(SEARCH("client", C185)), "Client", IF(ISNUMBER(SEARCH("Client", C185)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C185)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C185)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
+      <c r="R185" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="186" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
@@ -9615,6 +10334,9 @@
         <f t="shared" si="49"/>
         <v>Client</v>
       </c>
+      <c r="R186" s="5" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="187" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
@@ -9648,6 +10370,9 @@
         <f t="shared" ref="P187" si="105">IF(ISNUMBER(SEARCH("server", C187)), "Server", IF(ISNUMBER(SEARCH("Server", C187)), "Server", IF(ISNUMBER(SEARCH("client", C187)), "Client", IF(ISNUMBER(SEARCH("Client", C187)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C187)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C187)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
+      <c r="R187" s="5" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="188" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
@@ -9681,6 +10406,9 @@
         <f>IF(ISNUMBER(SEARCH("server", C188)), "Server", IF(ISNUMBER(SEARCH("Server", C188)), "Server", IF(ISNUMBER(SEARCH("client", C188)), "Client", IF(ISNUMBER(SEARCH("Client", C188)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C188)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C188)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
+      <c r="R188" s="5" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="189" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
@@ -9717,6 +10445,9 @@
         <f t="shared" ref="P189" si="107">IF(ISNUMBER(SEARCH("server", C189)), "Server", IF(ISNUMBER(SEARCH("Server", C189)), "Server", IF(ISNUMBER(SEARCH("client", C189)), "Client", IF(ISNUMBER(SEARCH("Client", C189)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C189)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C189)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
+      <c r="R189" s="5" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="190" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
@@ -9789,6 +10520,12 @@
         <f t="shared" ref="P191" si="111">IF(ISNUMBER(SEARCH("server", C191)), "Server", IF(ISNUMBER(SEARCH("Server", C191)), "Server", IF(ISNUMBER(SEARCH("client", C191)), "Client", IF(ISNUMBER(SEARCH("Client", C191)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C191)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C191)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
+      <c r="R191" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="V191" s="5" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="192" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
@@ -9800,7 +10537,7 @@
       </c>
       <c r="F192" s="30"/>
     </row>
-    <row r="193" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>192</v>
       </c>
@@ -9832,8 +10569,11 @@
         <f t="shared" ref="P193" si="113">IF(ISNUMBER(SEARCH("server", C193)), "Server", IF(ISNUMBER(SEARCH("Server", C193)), "Server", IF(ISNUMBER(SEARCH("client", C193)), "Client", IF(ISNUMBER(SEARCH("Client", C193)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C193)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C193)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="194" spans="1:16" ht="64" x14ac:dyDescent="0.2">
+      <c r="R193" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -9865,8 +10605,11 @@
         <f t="shared" ref="P194" si="115">IF(ISNUMBER(SEARCH("server", C194)), "Server", IF(ISNUMBER(SEARCH("Server", C194)), "Server", IF(ISNUMBER(SEARCH("client", C194)), "Client", IF(ISNUMBER(SEARCH("Client", C194)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C194)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C194)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="195" spans="1:16" ht="64" x14ac:dyDescent="0.2">
+      <c r="R194" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>194</v>
       </c>
@@ -9898,8 +10641,11 @@
         <f t="shared" ref="P195:P199" si="117">IF(ISNUMBER(SEARCH("server", C195)), "Server", IF(ISNUMBER(SEARCH("Server", C195)), "Server", IF(ISNUMBER(SEARCH("client", C195)), "Client", IF(ISNUMBER(SEARCH("Client", C195)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C195)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C195)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="196" spans="1:16" ht="64" x14ac:dyDescent="0.2">
+      <c r="R195" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -9931,8 +10677,11 @@
         <f t="shared" si="117"/>
         <v/>
       </c>
-    </row>
-    <row r="197" spans="1:16" ht="64" x14ac:dyDescent="0.2">
+      <c r="R196" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -9964,8 +10713,11 @@
         <f t="shared" si="117"/>
         <v/>
       </c>
-    </row>
-    <row r="198" spans="1:16" ht="64" x14ac:dyDescent="0.2">
+      <c r="R197" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -9997,8 +10749,11 @@
         <f t="shared" si="117"/>
         <v/>
       </c>
-    </row>
-    <row r="199" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R198" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>198</v>
       </c>
@@ -10030,8 +10785,11 @@
         <f t="shared" si="117"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="200" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R199" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -10063,8 +10821,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C200)), "Server", IF(ISNUMBER(SEARCH("Server", C200)), "Server", IF(ISNUMBER(SEARCH("client", C200)), "Client", IF(ISNUMBER(SEARCH("Client", C200)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C200)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C200)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="201" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+      <c r="R200" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>200</v>
       </c>
@@ -10073,7 +10834,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>201</v>
       </c>
@@ -10082,7 +10843,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>202</v>
       </c>
@@ -10114,8 +10875,11 @@
         <f t="shared" si="49"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="204" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="R203" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" ht="119" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>203</v>
       </c>
@@ -10147,8 +10911,11 @@
         <f t="shared" ref="P204" si="119">IF(ISNUMBER(SEARCH("server", C204)), "Server", IF(ISNUMBER(SEARCH("Server", C204)), "Server", IF(ISNUMBER(SEARCH("client", C204)), "Client", IF(ISNUMBER(SEARCH("Client", C204)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C204)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C204)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="205" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R204" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>204</v>
       </c>
@@ -10180,8 +10947,11 @@
         <f t="shared" ref="P205" si="121">IF(ISNUMBER(SEARCH("server", C205)), "Server", IF(ISNUMBER(SEARCH("Server", C205)), "Server", IF(ISNUMBER(SEARCH("client", C205)), "Client", IF(ISNUMBER(SEARCH("Client", C205)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C205)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C205)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="206" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R205" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>205</v>
       </c>
@@ -10213,8 +10983,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C206)), "Server", IF(ISNUMBER(SEARCH("Server", C206)), "Server", IF(ISNUMBER(SEARCH("client", C206)), "Client", IF(ISNUMBER(SEARCH("Client", C206)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C206)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C206)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="207" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R206" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>206</v>
       </c>
@@ -10246,8 +11019,11 @@
         <f t="shared" ref="P207" si="123">IF(ISNUMBER(SEARCH("server", C207)), "Server", IF(ISNUMBER(SEARCH("Server", C207)), "Server", IF(ISNUMBER(SEARCH("client", C207)), "Client", IF(ISNUMBER(SEARCH("Client", C207)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C207)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C207)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="208" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R207" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>207</v>
       </c>
@@ -10279,8 +11055,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C208)), "Server", IF(ISNUMBER(SEARCH("Server", C208)), "Server", IF(ISNUMBER(SEARCH("client", C208)), "Client", IF(ISNUMBER(SEARCH("Client", C208)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C208)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C208)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="209" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+      <c r="R208" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" ht="204" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>208</v>
       </c>
@@ -10312,8 +11091,11 @@
         <f t="shared" ref="P209" si="125">IF(ISNUMBER(SEARCH("server", C209)), "Server", IF(ISNUMBER(SEARCH("Server", C209)), "Server", IF(ISNUMBER(SEARCH("client", C209)), "Client", IF(ISNUMBER(SEARCH("Client", C209)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C209)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C209)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="210" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R209" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -10345,8 +11127,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C210)), "Server", IF(ISNUMBER(SEARCH("Server", C210)), "Server", IF(ISNUMBER(SEARCH("client", C210)), "Client", IF(ISNUMBER(SEARCH("Client", C210)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C210)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C210)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="211" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R210" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>210</v>
       </c>
@@ -10378,8 +11163,11 @@
         <f t="shared" ref="P211" si="127">IF(ISNUMBER(SEARCH("server", C211)), "Server", IF(ISNUMBER(SEARCH("Server", C211)), "Server", IF(ISNUMBER(SEARCH("client", C211)), "Client", IF(ISNUMBER(SEARCH("Client", C211)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C211)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C211)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="212" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R211" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -10411,8 +11199,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C212)), "Server", IF(ISNUMBER(SEARCH("Server", C212)), "Server", IF(ISNUMBER(SEARCH("client", C212)), "Client", IF(ISNUMBER(SEARCH("Client", C212)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C212)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C212)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="213" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R212" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>212</v>
       </c>
@@ -10444,8 +11235,11 @@
         <f t="shared" ref="P213" si="129">IF(ISNUMBER(SEARCH("server", C213)), "Server", IF(ISNUMBER(SEARCH("Server", C213)), "Server", IF(ISNUMBER(SEARCH("client", C213)), "Client", IF(ISNUMBER(SEARCH("Client", C213)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C213)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C213)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="214" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R213" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -10477,8 +11271,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C214)), "Server", IF(ISNUMBER(SEARCH("Server", C214)), "Server", IF(ISNUMBER(SEARCH("client", C214)), "Client", IF(ISNUMBER(SEARCH("Client", C214)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C214)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C214)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="215" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+      <c r="R214" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" ht="102" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>214</v>
       </c>
@@ -10510,8 +11307,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C215)), "Server", IF(ISNUMBER(SEARCH("Server", C215)), "Server", IF(ISNUMBER(SEARCH("client", C215)), "Client", IF(ISNUMBER(SEARCH("Client", C215)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C215)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C215)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="216" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+      <c r="R215" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -10543,8 +11343,11 @@
         <f t="shared" ref="P216" si="131">IF(ISNUMBER(SEARCH("server", C216)), "Server", IF(ISNUMBER(SEARCH("Server", C216)), "Server", IF(ISNUMBER(SEARCH("client", C216)), "Client", IF(ISNUMBER(SEARCH("Client", C216)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C216)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C216)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="217" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R216" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>216</v>
       </c>
@@ -10576,8 +11379,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C217)), "Server", IF(ISNUMBER(SEARCH("Server", C217)), "Server", IF(ISNUMBER(SEARCH("client", C217)), "Client", IF(ISNUMBER(SEARCH("Client", C217)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C217)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C217)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="218" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="R217" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" ht="136" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -10609,8 +11415,11 @@
         <f t="shared" ref="P218" si="133">IF(ISNUMBER(SEARCH("server", C218)), "Server", IF(ISNUMBER(SEARCH("Server", C218)), "Server", IF(ISNUMBER(SEARCH("client", C218)), "Client", IF(ISNUMBER(SEARCH("Client", C218)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C218)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C218)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="219" spans="1:16" ht="306" x14ac:dyDescent="0.2">
+      <c r="R218" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" ht="306" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>218</v>
       </c>
@@ -10642,8 +11451,11 @@
         <f t="shared" ref="P219" si="135">IF(ISNUMBER(SEARCH("server", C219)), "Server", IF(ISNUMBER(SEARCH("Server", C219)), "Server", IF(ISNUMBER(SEARCH("client", C219)), "Client", IF(ISNUMBER(SEARCH("Client", C219)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C219)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C219)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="220" spans="1:16" ht="176.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R219" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" ht="176.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -10678,8 +11490,11 @@
         <f t="shared" ref="P220" si="137">IF(ISNUMBER(SEARCH("server", C220)), "Server", IF(ISNUMBER(SEARCH("Server", C220)), "Server", IF(ISNUMBER(SEARCH("client", C220)), "Client", IF(ISNUMBER(SEARCH("Client", C220)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C220)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C220)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="221" spans="1:16" ht="176.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R220" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" ht="176.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>220</v>
       </c>
@@ -10714,8 +11529,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C221)), "Server", IF(ISNUMBER(SEARCH("Server", C221)), "Server", IF(ISNUMBER(SEARCH("client", C221)), "Client", IF(ISNUMBER(SEARCH("Client", C221)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C221)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C221)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="222" spans="1:16" ht="176.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R221" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" ht="176.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -10747,8 +11565,11 @@
         <f t="shared" ref="P222" si="139">IF(ISNUMBER(SEARCH("server", C222)), "Server", IF(ISNUMBER(SEARCH("Server", C222)), "Server", IF(ISNUMBER(SEARCH("client", C222)), "Client", IF(ISNUMBER(SEARCH("Client", C222)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C222)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C222)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="223" spans="1:16" ht="218.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R222" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" ht="218.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>222</v>
       </c>
@@ -10780,8 +11601,11 @@
         <f t="shared" ref="P223" si="141">IF(ISNUMBER(SEARCH("server", C223)), "Server", IF(ISNUMBER(SEARCH("Server", C223)), "Server", IF(ISNUMBER(SEARCH("client", C223)), "Client", IF(ISNUMBER(SEARCH("Client", C223)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C223)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C223)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="224" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R223" s="5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -10813,8 +11637,11 @@
         <f t="shared" ref="P224" si="143">IF(ISNUMBER(SEARCH("server", C224)), "Server", IF(ISNUMBER(SEARCH("Server", C224)), "Server", IF(ISNUMBER(SEARCH("client", C224)), "Client", IF(ISNUMBER(SEARCH("Client", C224)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C224)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C224)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="225" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R224" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="225" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -10846,8 +11673,11 @@
         <f t="shared" ref="P225" si="145">IF(ISNUMBER(SEARCH("server", C225)), "Server", IF(ISNUMBER(SEARCH("Server", C225)), "Server", IF(ISNUMBER(SEARCH("client", C225)), "Client", IF(ISNUMBER(SEARCH("Client", C225)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C225)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C225)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="226" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R225" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="226" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -10879,8 +11709,11 @@
         <f t="shared" ref="P226" si="147">IF(ISNUMBER(SEARCH("server", C226)), "Server", IF(ISNUMBER(SEARCH("Server", C226)), "Server", IF(ISNUMBER(SEARCH("client", C226)), "Client", IF(ISNUMBER(SEARCH("Client", C226)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C226)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C226)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="227" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R226" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="227" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>226</v>
       </c>
@@ -10912,8 +11745,11 @@
         <f t="shared" ref="P227:P229" si="149">IF(ISNUMBER(SEARCH("server", C227)), "Server", IF(ISNUMBER(SEARCH("Server", C227)), "Server", IF(ISNUMBER(SEARCH("client", C227)), "Client", IF(ISNUMBER(SEARCH("Client", C227)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C227)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C227)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="228" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R227" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="228" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>227</v>
       </c>
@@ -10945,8 +11781,11 @@
         <f t="shared" si="149"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="229" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R228" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="229" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>228</v>
       </c>
@@ -10978,8 +11817,11 @@
         <f t="shared" si="149"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="230" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R229" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="230" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>229</v>
       </c>
@@ -11011,8 +11853,14 @@
         <f t="shared" ref="P230" si="151">IF(ISNUMBER(SEARCH("server", C230)), "Server", IF(ISNUMBER(SEARCH("Server", C230)), "Server", IF(ISNUMBER(SEARCH("client", C230)), "Client", IF(ISNUMBER(SEARCH("Client", C230)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C230)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C230)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="231" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R230" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="V230" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="231" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>230</v>
       </c>
@@ -11044,8 +11892,11 @@
         <f t="shared" ref="P231" si="153">IF(ISNUMBER(SEARCH("server", C231)), "Server", IF(ISNUMBER(SEARCH("Server", C231)), "Server", IF(ISNUMBER(SEARCH("client", C231)), "Client", IF(ISNUMBER(SEARCH("Client", C231)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C231)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C231)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="232" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R231" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="232" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -11080,8 +11931,11 @@
         <f t="shared" ref="P232" si="155">IF(ISNUMBER(SEARCH("server", C232)), "Server", IF(ISNUMBER(SEARCH("Server", C232)), "Server", IF(ISNUMBER(SEARCH("client", C232)), "Client", IF(ISNUMBER(SEARCH("Client", C232)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C232)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C232)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="233" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R232" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="233" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>232</v>
       </c>
@@ -11105,8 +11959,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C233)), "Server", IF(ISNUMBER(SEARCH("Server", C233)), "Server", IF(ISNUMBER(SEARCH("client", C233)), "Client", IF(ISNUMBER(SEARCH("Client", C233)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C233)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C233)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="234" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R233" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="234" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -11130,8 +11987,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C234)), "Server", IF(ISNUMBER(SEARCH("Server", C234)), "Server", IF(ISNUMBER(SEARCH("client", C234)), "Client", IF(ISNUMBER(SEARCH("Client", C234)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C234)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C234)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="235" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R234" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="235" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>234</v>
       </c>
@@ -11163,8 +12023,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C235)), "Server", IF(ISNUMBER(SEARCH("Server", C235)), "Server", IF(ISNUMBER(SEARCH("client", C235)), "Client", IF(ISNUMBER(SEARCH("Client", C235)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C235)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C235)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="236" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R235" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="236" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -11196,8 +12059,11 @@
         <f t="shared" ref="P236" si="157">IF(ISNUMBER(SEARCH("server", C236)), "Server", IF(ISNUMBER(SEARCH("Server", C236)), "Server", IF(ISNUMBER(SEARCH("client", C236)), "Client", IF(ISNUMBER(SEARCH("Client", C236)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C236)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C236)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="237" spans="1:16" ht="181.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R236" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="237" spans="1:22" ht="181.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>236</v>
       </c>
@@ -11221,8 +12087,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C237)), "Server", IF(ISNUMBER(SEARCH("Server", C237)), "Server", IF(ISNUMBER(SEARCH("client", C237)), "Client", IF(ISNUMBER(SEARCH("Client", C237)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C237)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C237)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="238" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R237" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="238" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -11246,8 +12115,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C238)), "Server", IF(ISNUMBER(SEARCH("Server", C238)), "Server", IF(ISNUMBER(SEARCH("client", C238)), "Client", IF(ISNUMBER(SEARCH("Client", C238)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C238)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C238)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="239" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R238" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="239" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>238</v>
       </c>
@@ -11279,8 +12151,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C239)), "Server", IF(ISNUMBER(SEARCH("Server", C239)), "Server", IF(ISNUMBER(SEARCH("client", C239)), "Client", IF(ISNUMBER(SEARCH("Client", C239)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C239)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C239)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="240" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R239" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="240" spans="1:22" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -11312,8 +12187,11 @@
         <f t="shared" ref="P240" si="159">IF(ISNUMBER(SEARCH("server", C240)), "Server", IF(ISNUMBER(SEARCH("Server", C240)), "Server", IF(ISNUMBER(SEARCH("client", C240)), "Client", IF(ISNUMBER(SEARCH("Client", C240)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C240)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C240)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="241" spans="1:16" ht="179.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R240" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" ht="179.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>240</v>
       </c>
@@ -11345,8 +12223,11 @@
         <f t="shared" ref="P241" si="161">IF(ISNUMBER(SEARCH("server", C241)), "Server", IF(ISNUMBER(SEARCH("Server", C241)), "Server", IF(ISNUMBER(SEARCH("client", C241)), "Client", IF(ISNUMBER(SEARCH("Client", C241)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C241)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C241)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="242" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R241" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -11384,8 +12265,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C242)), "Server", IF(ISNUMBER(SEARCH("Server", C242)), "Server", IF(ISNUMBER(SEARCH("client", C242)), "Client", IF(ISNUMBER(SEARCH("Client", C242)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C242)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C242)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="243" spans="1:16" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R242" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" ht="178.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>242</v>
       </c>
@@ -11409,8 +12293,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C243)), "Server", IF(ISNUMBER(SEARCH("Server", C243)), "Server", IF(ISNUMBER(SEARCH("client", C243)), "Client", IF(ISNUMBER(SEARCH("Client", C243)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C243)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C243)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="244" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R243" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -11442,8 +12329,11 @@
         <f t="shared" ref="P244" si="163">IF(ISNUMBER(SEARCH("server", C244)), "Server", IF(ISNUMBER(SEARCH("Server", C244)), "Server", IF(ISNUMBER(SEARCH("client", C244)), "Client", IF(ISNUMBER(SEARCH("Client", C244)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C244)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C244)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="245" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R244" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>244</v>
       </c>
@@ -11475,8 +12365,11 @@
         <f t="shared" ref="P245" si="165">IF(ISNUMBER(SEARCH("server", C245)), "Server", IF(ISNUMBER(SEARCH("Server", C245)), "Server", IF(ISNUMBER(SEARCH("client", C245)), "Client", IF(ISNUMBER(SEARCH("Client", C245)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C245)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C245)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="246" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R245" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -11511,8 +12404,11 @@
         <f t="shared" ref="P246" si="167">IF(ISNUMBER(SEARCH("server", C246)), "Server", IF(ISNUMBER(SEARCH("Server", C246)), "Server", IF(ISNUMBER(SEARCH("client", C246)), "Client", IF(ISNUMBER(SEARCH("Client", C246)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C246)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C246)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="247" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+      <c r="R246" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>246</v>
       </c>
@@ -11536,8 +12432,11 @@
         <f t="shared" ref="P247:P256" si="169">IF(ISNUMBER(SEARCH("server", C247)), "Server", IF(ISNUMBER(SEARCH("Server", C247)), "Server", IF(ISNUMBER(SEARCH("client", C247)), "Client", IF(ISNUMBER(SEARCH("Client", C247)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C247)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C247)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="248" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R247" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -11561,8 +12460,11 @@
         <f t="shared" si="169"/>
         <v/>
       </c>
-    </row>
-    <row r="249" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R248" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>248</v>
       </c>
@@ -11586,8 +12488,11 @@
         <f t="shared" si="169"/>
         <v/>
       </c>
-    </row>
-    <row r="250" spans="1:16" ht="121.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R249" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" ht="121.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>249</v>
       </c>
@@ -11611,8 +12516,11 @@
         <f t="shared" si="169"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="251" spans="1:16" ht="148.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R250" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" ht="148.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>250</v>
       </c>
@@ -11636,8 +12544,11 @@
         <f t="shared" si="169"/>
         <v/>
       </c>
-    </row>
-    <row r="252" spans="1:16" ht="148.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R251" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" ht="148.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>251</v>
       </c>
@@ -11661,8 +12572,11 @@
         <f t="shared" si="169"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="253" spans="1:16" ht="163.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R252" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" ht="163.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>252</v>
       </c>
@@ -11686,8 +12600,11 @@
         <f t="shared" si="169"/>
         <v/>
       </c>
-    </row>
-    <row r="254" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R253" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>253</v>
       </c>
@@ -11711,8 +12628,11 @@
         <f t="shared" si="169"/>
         <v/>
       </c>
-    </row>
-    <row r="255" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R254" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>254</v>
       </c>
@@ -11736,8 +12656,11 @@
         <f t="shared" si="169"/>
         <v/>
       </c>
-    </row>
-    <row r="256" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R255" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>255</v>
       </c>
@@ -11761,8 +12684,11 @@
         <f t="shared" si="169"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="257" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R256" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>256</v>
       </c>
@@ -11794,8 +12720,11 @@
         <f t="shared" ref="P257" si="171">IF(ISNUMBER(SEARCH("server", C257)), "Server", IF(ISNUMBER(SEARCH("Server", C257)), "Server", IF(ISNUMBER(SEARCH("client", C257)), "Client", IF(ISNUMBER(SEARCH("Client", C257)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C257)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C257)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="258" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R257" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>257</v>
       </c>
@@ -11830,8 +12759,11 @@
         <f t="shared" ref="P258" si="173">IF(ISNUMBER(SEARCH("server", C258)), "Server", IF(ISNUMBER(SEARCH("Server", C258)), "Server", IF(ISNUMBER(SEARCH("client", C258)), "Client", IF(ISNUMBER(SEARCH("Client", C258)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C258)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C258)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="259" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R258" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>258</v>
       </c>
@@ -11863,8 +12795,11 @@
         <f t="shared" ref="P259:P279" si="175">IF(ISNUMBER(SEARCH("server", C259)), "Server", IF(ISNUMBER(SEARCH("Server", C259)), "Server", IF(ISNUMBER(SEARCH("client", C259)), "Client", IF(ISNUMBER(SEARCH("Client", C259)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C259)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C259)), "Client", ""))))))</f>
         <v>Server</v>
       </c>
-    </row>
-    <row r="260" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R259" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>259</v>
       </c>
@@ -11896,8 +12831,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="261" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R260" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>260</v>
       </c>
@@ -11929,8 +12867,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="262" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R261" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>261</v>
       </c>
@@ -11962,8 +12903,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="263" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R262" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>262</v>
       </c>
@@ -11995,8 +12939,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="264" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R263" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>263</v>
       </c>
@@ -12028,8 +12975,11 @@
         <f t="shared" si="175"/>
         <v/>
       </c>
-    </row>
-    <row r="265" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R264" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>264</v>
       </c>
@@ -12061,8 +13011,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="266" spans="1:16" ht="208.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R265" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" ht="208.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>265</v>
       </c>
@@ -12094,8 +13047,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="267" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R266" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>266</v>
       </c>
@@ -12127,8 +13083,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="268" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R267" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>267</v>
       </c>
@@ -12160,8 +13119,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="269" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R268" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>268</v>
       </c>
@@ -12193,8 +13155,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="270" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R269" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>269</v>
       </c>
@@ -12226,8 +13191,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="271" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R270" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>270</v>
       </c>
@@ -12259,8 +13227,11 @@
         <f t="shared" si="175"/>
         <v/>
       </c>
-    </row>
-    <row r="272" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R271" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>271</v>
       </c>
@@ -12292,8 +13263,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="273" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R272" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>272</v>
       </c>
@@ -12325,8 +13299,11 @@
         <f t="shared" si="175"/>
         <v/>
       </c>
-    </row>
-    <row r="274" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R273" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>273</v>
       </c>
@@ -12358,8 +13335,11 @@
         <f t="shared" si="175"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="275" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R274" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>274</v>
       </c>
@@ -12391,8 +13371,11 @@
         <f t="shared" si="175"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="276" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R275" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>275</v>
       </c>
@@ -12424,8 +13407,11 @@
         <f t="shared" si="175"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="277" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R276" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>276</v>
       </c>
@@ -12457,8 +13443,11 @@
         <f t="shared" si="175"/>
         <v/>
       </c>
-    </row>
-    <row r="278" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R277" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>277</v>
       </c>
@@ -12490,8 +13479,11 @@
         <f t="shared" si="175"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="279" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R278" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>278</v>
       </c>
@@ -12523,8 +13515,11 @@
         <f t="shared" si="175"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="280" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R279" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>279</v>
       </c>
@@ -12559,8 +13554,11 @@
         <f t="shared" ref="P280" si="177">IF(ISNUMBER(SEARCH("server", C280)), "Server", IF(ISNUMBER(SEARCH("Server", C280)), "Server", IF(ISNUMBER(SEARCH("client", C280)), "Client", IF(ISNUMBER(SEARCH("Client", C280)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C280)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C280)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="281" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R280" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>280</v>
       </c>
@@ -12595,8 +13593,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C281)), "Server", IF(ISNUMBER(SEARCH("Server", C281)), "Server", IF(ISNUMBER(SEARCH("client", C281)), "Client", IF(ISNUMBER(SEARCH("Client", C281)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C281)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C281)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="282" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R281" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>281</v>
       </c>
@@ -12628,8 +13629,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C282)), "Server", IF(ISNUMBER(SEARCH("Server", C282)), "Server", IF(ISNUMBER(SEARCH("client", C282)), "Client", IF(ISNUMBER(SEARCH("Client", C282)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C282)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C282)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="283" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R282" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>282</v>
       </c>
@@ -12661,8 +13665,11 @@
         <f t="shared" ref="P283" si="179">IF(ISNUMBER(SEARCH("server", C283)), "Server", IF(ISNUMBER(SEARCH("Server", C283)), "Server", IF(ISNUMBER(SEARCH("client", C283)), "Client", IF(ISNUMBER(SEARCH("Client", C283)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C283)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C283)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="284" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R283" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>283</v>
       </c>
@@ -12686,8 +13693,11 @@
         <f t="shared" ref="P284:P291" si="181">IF(ISNUMBER(SEARCH("server", C284)), "Server", IF(ISNUMBER(SEARCH("Server", C284)), "Server", IF(ISNUMBER(SEARCH("client", C284)), "Client", IF(ISNUMBER(SEARCH("Client", C284)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C284)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C284)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="285" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R284" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>284</v>
       </c>
@@ -12711,8 +13721,11 @@
         <f t="shared" si="181"/>
         <v/>
       </c>
-    </row>
-    <row r="286" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R285" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>285</v>
       </c>
@@ -12736,8 +13749,11 @@
         <f t="shared" si="181"/>
         <v/>
       </c>
-    </row>
-    <row r="287" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R286" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>286</v>
       </c>
@@ -12761,8 +13777,11 @@
         <f t="shared" si="181"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="288" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R287" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>287</v>
       </c>
@@ -12786,8 +13805,11 @@
         <f t="shared" si="181"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="289" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R288" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>288</v>
       </c>
@@ -12811,8 +13833,11 @@
         <f t="shared" si="181"/>
         <v>Server</v>
       </c>
-    </row>
-    <row r="290" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R289" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>289</v>
       </c>
@@ -12836,8 +13861,11 @@
         <f t="shared" si="181"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="291" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R290" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>290</v>
       </c>
@@ -12861,8 +13889,11 @@
         <f t="shared" si="181"/>
         <v>Client</v>
       </c>
-    </row>
-    <row r="292" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R291" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>291</v>
       </c>
@@ -12894,8 +13925,11 @@
         <f t="shared" ref="P292" si="183">IF(ISNUMBER(SEARCH("server", C292)), "Server", IF(ISNUMBER(SEARCH("Server", C292)), "Server", IF(ISNUMBER(SEARCH("client", C292)), "Client", IF(ISNUMBER(SEARCH("Client", C292)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C292)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C292)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="293" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R292" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>292</v>
       </c>
@@ -12927,8 +13961,11 @@
         <f t="shared" ref="P293" si="185">IF(ISNUMBER(SEARCH("server", C293)), "Server", IF(ISNUMBER(SEARCH("Server", C293)), "Server", IF(ISNUMBER(SEARCH("client", C293)), "Client", IF(ISNUMBER(SEARCH("Client", C293)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C293)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C293)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="294" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R293" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>293</v>
       </c>
@@ -12960,8 +13997,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C294)), "Server", IF(ISNUMBER(SEARCH("Server", C294)), "Server", IF(ISNUMBER(SEARCH("client", C294)), "Client", IF(ISNUMBER(SEARCH("Client", C294)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C294)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C294)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="295" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R294" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>294</v>
       </c>
@@ -12993,8 +14033,11 @@
         <f>IF(ISNUMBER(SEARCH("server", C295)), "Server", IF(ISNUMBER(SEARCH("Server", C295)), "Server", IF(ISNUMBER(SEARCH("client", C295)), "Client", IF(ISNUMBER(SEARCH("Client", C295)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C295)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C295)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="296" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R295" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>295</v>
       </c>
@@ -13026,8 +14069,11 @@
         <f t="shared" ref="P296" si="187">IF(ISNUMBER(SEARCH("server", C296)), "Server", IF(ISNUMBER(SEARCH("Server", C296)), "Server", IF(ISNUMBER(SEARCH("client", C296)), "Client", IF(ISNUMBER(SEARCH("Client", C296)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C296)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C296)), "Client", ""))))))</f>
         <v/>
       </c>
-    </row>
-    <row r="297" spans="1:16" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R296" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" ht="183.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>296</v>
       </c>
@@ -13059,8 +14105,11 @@
         <f t="shared" ref="P297" si="189">IF(ISNUMBER(SEARCH("server", C297)), "Server", IF(ISNUMBER(SEARCH("Server", C297)), "Server", IF(ISNUMBER(SEARCH("client", C297)), "Client", IF(ISNUMBER(SEARCH("Client", C297)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C297)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C297)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="298" spans="1:16" ht="272" x14ac:dyDescent="0.2">
+      <c r="R297" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" ht="272" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>297</v>
       </c>
@@ -13092,8 +14141,11 @@
         <f t="shared" ref="P298" si="191">IF(ISNUMBER(SEARCH("server", C298)), "Server", IF(ISNUMBER(SEARCH("Server", C298)), "Server", IF(ISNUMBER(SEARCH("client", C298)), "Client", IF(ISNUMBER(SEARCH("Client", C298)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C298)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C298)), "Client", ""))))))</f>
         <v>Client</v>
       </c>
-    </row>
-    <row r="299" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+      <c r="R298" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="M299" s="31" t="str" cm="1">
         <f t="array" ref="M299">PAGE_NAME(B299)</f>
         <v/>
@@ -13103,7 +14155,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="M300" s="31" t="str" cm="1">
         <f t="array" ref="M300">PAGE_NAME(B300)</f>
         <v/>
@@ -13113,7 +14165,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="M301" s="31" t="str" cm="1">
         <f t="array" ref="M301">PAGE_NAME(B301)</f>
         <v/>
@@ -13123,7 +14175,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="M302" s="31" t="str" cm="1">
         <f t="array" ref="M302">PAGE_NAME(B302)</f>
         <v/>
@@ -13133,7 +14185,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="M303" s="31" t="str" cm="1">
         <f t="array" ref="M303">PAGE_NAME(B303)</f>
         <v/>
@@ -13143,7 +14195,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="M304" s="31" t="str" cm="1">
         <f t="array" ref="M304">PAGE_NAME(B304)</f>
         <v/>
@@ -14940,24 +15992,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323F474-BE25-4449-9222-E1A46A1843B5}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" customWidth="1"/>
     <col min="2" max="2" width="56.5" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
-        <v>436</v>
-      </c>
-      <c r="B1" s="44"/>
-    </row>
-    <row r="2" spans="1:2" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="45" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="45"/>
+    </row>
+    <row r="2" spans="1:6" ht="82" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>403</v>
       </c>
@@ -14965,12 +16017,12 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>406</v>
       </c>
@@ -14978,12 +16030,12 @@
         <v>407</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>409</v>
       </c>
@@ -14991,32 +16043,33 @@
         <v>410</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="F11" s="27"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>416</v>
       </c>
@@ -15024,12 +16077,20 @@
         <v>417</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="68" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>418</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>419</v>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="255" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -15054,16 +16115,16 @@
         <v>406</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -15071,13 +16132,13 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C2" t="s">
         <v>424</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>425</v>
-      </c>
-      <c r="D2" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -15085,13 +16146,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="D3" t="s">
         <v>428</v>
-      </c>
-      <c r="D3" t="s">
-        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -15109,7 +16170,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B1" t="s">
         <v>12</v>
@@ -15129,10 +16190,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D2" t="s">
         <v>431</v>
-      </c>
-      <c r="D2" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -15143,10 +16204,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D3" t="s">
         <v>433</v>
-      </c>
-      <c r="D3" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -15154,7 +16215,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -15432,15 +16493,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
@@ -15451,6 +16503,15 @@
     <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15474,14 +16535,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -15497,4 +16550,12 @@
     <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>